--- a/config/rules/.history/CRS620MI.xlsx
+++ b/config/rules/.history/CRS620MI.xlsx
@@ -535,6 +535,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -550,6 +551,9 @@
           <t>ABS class supplier</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -590,6 +594,9 @@
           <t>ABC method supplier</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,6 +619,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -627,6 +635,9 @@
           <t>User-defined accounting control object</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -677,6 +688,9 @@
           <t>Address number</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -699,6 +713,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -714,6 +729,9 @@
           <t>Address line 1</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -736,6 +754,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -751,6 +770,9 @@
           <t>Address line 2</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -773,6 +795,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -788,6 +811,9 @@
           <t>Address line 3</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -810,6 +836,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -825,6 +852,9 @@
           <t>Address line 4</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -847,6 +877,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -862,6 +893,9 @@
           <t>Address type</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -884,6 +918,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -899,6 +934,9 @@
           <t>Ship-via address</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -921,6 +959,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -936,6 +975,9 @@
           <t>Agent</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -978,6 +1020,9 @@
           <t>Consignment agreement</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1000,6 +1045,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1015,6 +1061,9 @@
           <t>Search key</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1057,6 +1106,9 @@
           <t>Attribute pricing rule</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1079,6 +1131,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1094,6 +1147,9 @@
           <t>Disable auto confirm - internal sales</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1116,6 +1172,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1131,6 +1188,9 @@
           <t>Auto verified</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1153,6 +1213,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1168,6 +1229,9 @@
           <t>Activity code</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1190,6 +1254,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1205,6 +1270,9 @@
           <t>Buyer</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1227,6 +1295,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1242,6 +1311,9 @@
           <t>User def field 1</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1264,6 +1336,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1279,6 +1352,9 @@
           <t>User-defined field 1 - item</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1301,6 +1377,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1316,6 +1393,9 @@
           <t>User-defined field 2 - item</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1338,6 +1418,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1353,6 +1434,9 @@
           <t>User def field 3</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1375,6 +1459,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1390,6 +1475,9 @@
           <t>User def field 4</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1412,6 +1500,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1427,6 +1516,9 @@
           <t>User def field 5</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1449,6 +1541,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1464,6 +1557,9 @@
           <t>Consolidation group</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1486,6 +1582,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1501,6 +1598,9 @@
           <t>Claim invoice permitted</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1523,6 +1623,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1538,6 +1639,9 @@
           <t>Group of companies</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1560,6 +1664,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1575,6 +1680,9 @@
           <t>Organization No 2</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1597,6 +1705,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1612,6 +1721,9 @@
           <t>Organization No 1</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1654,6 +1766,9 @@
           <t>Exchange rate type</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1696,6 +1811,9 @@
           <t>Country</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1738,6 +1856,9 @@
           <t>Currency</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1760,6 +1881,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1775,6 +1897,9 @@
           <t>Custom Field (CMS080)</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1797,6 +1922,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1812,6 +1938,9 @@
           <t>Custom Field (CMS080)</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1834,6 +1963,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1849,6 +1979,9 @@
           <t>Custom Field (CMS080)</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1871,6 +2004,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1886,6 +2020,9 @@
           <t>Custom Field (CMS080)</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1908,6 +2045,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -1923,6 +2061,9 @@
           <t>Discount calculation method</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1967,6 +2108,9 @@
           <t>Alt Language</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2009,6 +2153,9 @@
           <t>Date type</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2051,6 +2198,9 @@
           <t>Date code</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2073,6 +2223,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2088,6 +2239,9 @@
           <t>Tolerance - delivery date</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2110,6 +2264,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2125,6 +2280,9 @@
           <t>Date format</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2149,17 +2307,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>cscd = str(row.get('CSCD', '')).strip().upper()
+          <t>cscd = str(row.get('CSCD', row.get('OKCSCD', ''))).strip().upper()
 ecar = '' if source is None else str(source).strip().upper()
-# Rule 1
 if cscd == 'CA' and ecar == '':
     return 'MB'
 if cscd == 'US' and ecar == '':
     return 'MN'
-# Rule 2
-#if cscd not in ['CA', 'US']:
-#    return '?'
-# Rule 3
 if ecar == 'PQ':
     return 'QC'
 return ecar</t>
@@ -2180,6 +2333,9 @@
           <t>State</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2202,6 +2358,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2217,6 +2374,9 @@
           <t>Place</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2239,6 +2399,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2254,6 +2415,9 @@
           <t>Date editing</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2276,6 +2440,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2291,6 +2456,9 @@
           <t>Electronic mail address</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2313,6 +2481,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2328,6 +2497,9 @@
           <t>County</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2350,6 +2522,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2365,6 +2538,9 @@
           <t>Monitoring activity list</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2387,6 +2563,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2402,6 +2579,9 @@
           <t>Forwarder SCAC</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2444,6 +2624,9 @@
           <t>Geographical code</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2466,6 +2649,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2481,6 +2665,9 @@
           <t>Geographic code X</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2503,6 +2690,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2518,6 +2706,9 @@
           <t>Geographic code Y</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2540,6 +2731,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2555,6 +2747,9 @@
           <t>Geographic code Z</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2577,6 +2772,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2592,6 +2788,9 @@
           <t>Group invoice</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2614,6 +2813,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2629,6 +2829,9 @@
           <t>Harbor/Airport</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2671,6 +2874,9 @@
           <t>Invoice approval condition 1</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2713,6 +2919,9 @@
           <t>Invoice approval condition 2</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2755,6 +2964,9 @@
           <t>Invoice approval condition 3</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2797,6 +3009,9 @@
           <t>Automatic invoice approval code</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2819,6 +3034,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2834,6 +3050,9 @@
           <t>Internal sales facility</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2856,6 +3075,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2871,6 +3091,9 @@
           <t>Not used</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2915,6 +3138,9 @@
           <t>Language</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2937,6 +3163,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -2952,6 +3179,9 @@
           <t>Media profile</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2994,6 +3224,9 @@
           <t>Delivery method</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3016,6 +3249,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3031,6 +3265,9 @@
           <t>Order type</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3053,6 +3290,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3068,6 +3306,9 @@
           <t>Our customer number at supplier</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3090,6 +3331,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3105,6 +3347,9 @@
           <t>Payment priority</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3127,6 +3372,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3142,6 +3388,9 @@
           <t>Telephone number 1</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3164,6 +3413,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3179,6 +3429,9 @@
           <t>Telephone number 2</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3201,6 +3454,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3216,6 +3470,9 @@
           <t>Telephone number 1</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3238,6 +3495,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3253,6 +3511,9 @@
           <t>Planning node</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3275,6 +3536,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3290,6 +3552,9 @@
           <t>Postal lead time - supplier</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3312,6 +3577,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3327,6 +3593,9 @@
           <t>Postal code</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3349,6 +3618,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3364,6 +3634,9 @@
           <t>Point of time table</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3386,6 +3659,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3401,6 +3675,9 @@
           <t>Print packing instruction</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3423,6 +3700,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3438,6 +3716,9 @@
           <t>Level of purchase planning</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3460,6 +3741,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3475,6 +3757,9 @@
           <t>Printout code</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3497,6 +3782,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3512,6 +3798,9 @@
           <t>Payee</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3534,6 +3823,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3549,6 +3839,9 @@
           <t>Pseudo identity</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3571,6 +3864,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3586,6 +3880,9 @@
           <t>Tolerance - payment</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3608,6 +3905,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3623,6 +3921,9 @@
           <t>PIN code</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3645,6 +3946,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3660,6 +3962,9 @@
           <t>Payment method - accounts payable</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3682,6 +3987,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3697,6 +4003,9 @@
           <t>Quality Class</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3719,6 +4028,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3734,6 +4044,9 @@
           <t>Rail Station</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3756,6 +4069,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3771,6 +4085,9 @@
           <t>Invoice accounting template</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3793,6 +4110,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3808,6 +4126,9 @@
           <t>Remark</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3830,6 +4151,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3845,6 +4167,9 @@
           <t>Authorized User</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3867,6 +4192,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3882,6 +4208,9 @@
           <t>Reference</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3904,6 +4233,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3919,6 +4249,9 @@
           <t>Reference type</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3941,6 +4274,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3956,6 +4290,9 @@
           <t>Supplier's address reference</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3978,6 +4315,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -3993,6 +4331,9 @@
           <t>Self-billing permitted</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4015,6 +4356,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4030,6 +4372,9 @@
           <t>Supplier rebate claim invoice permitted</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4052,6 +4397,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4067,6 +4413,9 @@
           <t>Claim inv setting ID - sup reb on purch</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4089,6 +4438,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4104,6 +4454,9 @@
           <t>Rebate claim invoice setting ID</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4126,6 +4479,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4141,6 +4495,9 @@
           <t>Supplier's customer number</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4163,6 +4520,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4178,6 +4536,9 @@
           <t>Service code</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4220,6 +4581,9 @@
           <t>Shipment advice</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4262,6 +4626,9 @@
           <t>Shipment table</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4284,6 +4651,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4299,6 +4667,9 @@
           <t>Monitoring class</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4321,6 +4692,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4336,6 +4708,9 @@
           <t>SPLC code</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4358,6 +4733,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4373,6 +4749,9 @@
           <t>Supplier rebate agreement model</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4395,6 +4774,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4410,6 +4790,9 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4432,6 +4815,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4447,6 +4831,9 @@
           <t>Start date</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4469,6 +4856,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4484,6 +4872,9 @@
           <t>Supplier alternate identity</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4506,6 +4897,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4521,6 +4913,9 @@
           <t>Supplier Group</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4543,6 +4938,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4558,6 +4954,9 @@
           <t>Supplier computer communication address</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4580,6 +4979,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4595,6 +4995,9 @@
           <t>Supplier no. in group/</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4617,6 +5020,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4632,6 +5036,9 @@
           <t>Statistical supplier</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4654,6 +5061,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4669,6 +5077,9 @@
           <t>Supplier name</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4711,6 +5122,9 @@
           <t>Supplier ID</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4733,6 +5147,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4748,6 +5163,9 @@
           <t>Supplier ID</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4770,6 +5188,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4785,6 +5204,9 @@
           <t>Supplier statistics</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4807,6 +5229,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4822,6 +5245,9 @@
           <t>Number of years of statistics</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4844,6 +5270,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4859,6 +5286,9 @@
           <t>Supplier type</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4881,6 +5311,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4896,6 +5327,9 @@
           <t>Supplying warehouse</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4938,6 +5372,9 @@
           <t>Tax withholding method</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4960,6 +5397,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -4975,6 +5413,9 @@
           <t>Tax code customer/address</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4997,6 +5438,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5012,6 +5454,9 @@
           <t>Trade code</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5034,6 +5479,7 @@
           <t>CONST</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5049,6 +5495,9 @@
           <t>Freight terms</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5071,6 +5520,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5086,6 +5536,9 @@
           <t>Cash discount term</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5108,6 +5561,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5123,6 +5577,9 @@
           <t>Delivery terms</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5165,6 +5622,9 @@
           <t>Packaging terms</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5187,6 +5647,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5202,6 +5663,9 @@
           <t>Payment terms</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5224,6 +5688,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5239,6 +5704,9 @@
           <t>Facsimile transmission number</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5261,6 +5729,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5276,6 +5745,9 @@
           <t>Tax ID number for supplier</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5298,6 +5770,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5313,6 +5786,9 @@
           <t>Tax ID for supplier</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5335,6 +5811,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5350,6 +5827,9 @@
           <t>Telex number</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5372,6 +5852,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5387,6 +5868,9 @@
           <t>City</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5429,6 +5913,9 @@
           <t>Tax applicable</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5451,6 +5938,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5466,6 +5954,9 @@
           <t>Tax included</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5488,6 +5979,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5503,6 +5995,9 @@
           <t>VAT Reg No. / ISO Cert</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5525,6 +6020,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5540,6 +6036,9 @@
           <t>VAT code</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5562,6 +6061,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5577,6 +6077,9 @@
           <t>Tax withholding percentage</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5599,6 +6102,7 @@
           <t>DIRECT</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5614,6 +6118,9 @@
           <t>Your reference</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5656,6 +6163,9 @@
           <t>Supplier ID</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5698,6 +6208,9 @@
           <t>Supplier ID</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5740,6 +6253,9 @@
           <t>Supplier ID</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5782,6 +6298,9 @@
           <t>Supplier ID</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5824,6 +6343,9 @@
           <t>Supplier ID</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5866,6 +6388,9 @@
           <t>Supplier ID</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5908,6 +6433,9 @@
           <t>Mapped from STEM</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11243,7 +11771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -13420,7 +13948,6 @@
           <t>ADD</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>New Rule Created</t>
@@ -13443,7 +13970,6 @@
           <t>DELETE</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Rule Deleted</t>
@@ -13736,7 +14262,6 @@
           <t>ADD</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>New Rule Created</t>
@@ -13759,7 +14284,6 @@
           <t>DELETE</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Rule Deleted</t>
@@ -14635,6 +15159,107 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:32:17</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ECAR</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Val: 'cscd = str(row.get('CSCD', '')).strip().upper()
+ecar = '' if source is None else str(source).strip().upper()
+# Rule 1
+if cscd == 'CA' and ecar == '':
+    return 'MB'
+if cscd == 'US' and ecar == '':
+    return 'MN'
+# Rule 2
+#if cscd not in ['CA', 'US']:
+#    return '?'
+# Rule 3
+if ecar == 'PQ':
+    return 'QC'
+return ecar'-&gt;'cscd = str(row.get('CSCD', row.get('OKCSCD', ''))).strip().upper()
+ecar = '' if source is None else str(source).strip().upper()
+# Rule 1
+if cscd == 'CA' and ecar == '':
+    return 'MB'
+if cscd == 'US' and ecar == '':
+    return 'MN'
+# Rule 2
+#if cscd not in ['CA', 'US']:
+#    return '?'
+# Rule 3
+if ecar == 'PQ':
+    return 'QC'
+return ecar'</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:33:30</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ECAR</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Val: 'cscd = str(row.get('CSCD', row.get('OKCSCD', ''))).strip().upper()
+ecar = '' if source is None else str(source).strip().upper()
+# Rule 1
+if cscd == 'CA' and ecar == '':
+    return 'MB'
+if cscd == 'US' and ecar == '':
+    return 'MN'
+# Rule 2
+#if cscd not in ['CA', 'US']:
+#    return '?'
+# Rule 3
+if ecar == 'PQ':
+    return 'QC'
+return ecar'-&gt;'cscd = str(row.get('CSCD', row.get('OKCSCD', ''))).strip().upper()
+ecar = '' if source is None else str(source).strip().upper()
+if cscd == 'CA' and ecar == '':
+    return 'MB'
+if cscd == 'US' and ecar == '':
+    return 'MN'
+if ecar == 'PQ':
+    return 'QC'
+return ecar'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
